--- a/SGC-CKN/Excel/ad38ec34-8745-4e53-8bf9-ac365698d95c_ĐÀI_TRÀ_P1-145_D800_28-05-2026.xlsx
+++ b/SGC-CKN/Excel/ad38ec34-8745-4e53-8bf9-ac365698d95c_ĐÀI_TRÀ_P1-145_D800_28-05-2026.xlsx
@@ -53,13 +53,13 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>02:40 28/05/2026</t>
+    <t>02:40 28/03/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>11:40 28/05/2026</t>
+    <t>11:40 28/03/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -99,11 +99,11 @@
   </si>
   <si>
     <t xml:space="preserve">02:40
-28/05/2026</t>
+28/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">02:55
-28/05/2026</t>
+28/03/2026</t>
   </si>
   <si>
     <t>Length calculated: 1.5 - 0.71 = 0.79</t>
@@ -112,11 +112,11 @@
     <t>2</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">03:15
-28/05/2026</t>
+28/03/2026</t>
   </si>
   <si>
     <t/>
@@ -125,11 +125,11 @@
     <t>3</t>
   </si>
   <si>
-    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
+    <t>Cát pha, xám ghi, xám nâu, xám vàng, TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">05:50
-28/05/2026</t>
+28/03/2026</t>
   </si>
   <si>
     <t>4</t>
@@ -139,41 +139,41 @@
   </si>
   <si>
     <t xml:space="preserve">06:20
-28/05/2026</t>
+28/03/2026</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>Sét xám vàng, nâu vàng, xám xanh TT nửa cứng</t>
+    <t>Sét xám vàng, nâu vàng, xám xanh, TT nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">07:10
-28/05/2026</t>
+28/03/2026</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">08:10
-28/05/2026</t>
+28/03/2026</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
-    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
+    <t>Cát thô, xám vàng, xám xanh, xám nâu, KC chặt</t>
   </si>
   <si>
     <t xml:space="preserve">08:00
-28/05/2026</t>
+28/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">10:05
-28/05/2026</t>
+28/03/2026</t>
   </si>
   <si>
     <t>Top number 29,89 at the line boundary</t>
@@ -182,11 +182,11 @@
     <t>8</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">11:40
-28/05/2026</t>
+28/03/2026</t>
   </si>
   <si>
     <t>Bottom depth 43.45; depth marker 36.45 noted in between</t>
